--- a/files/PINGPONG Command Reference_20191013_new.xlsx
+++ b/files/PINGPONG Command Reference_20191013_new.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\source\pingpong\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C859B4-23A8-499A-8081-510177DEDCC6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F500FB8-F039-41B9-BA3F-E1AF89398401}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="671" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="671" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="STATEMENTS" sheetId="26" r:id="rId1"/>
@@ -5672,6 +5672,81 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -5684,81 +5759,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -5780,6 +5780,18 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -5789,17 +5801,29 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -5823,136 +5847,112 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7137,26 +7137,26 @@
       </c>
       <c r="C12" s="33">
         <f ca="1">+IF(RANDBETWEEN(-1,1)=0,1,-1)</f>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D12" s="33">
         <v>1</v>
       </c>
       <c r="E12" s="2">
         <f t="shared" ref="E12:E44" ca="1" si="0">+RANDBETWEEN(900,1000)*C12</f>
-        <v>-955</v>
+        <v>906</v>
       </c>
       <c r="F12" s="2">
         <f ca="1">+RANDBETWEEN(200,500)</f>
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="G12" s="34" t="str">
         <f t="shared" ref="G12:G44" ca="1" si="1">+IF(MID(DEC2HEX(E12),7,2)="","00",MID(DEC2HEX(E12),7,2))</f>
-        <v>FC</v>
+        <v>00</v>
       </c>
       <c r="H12" s="34" t="str">
         <f ca="1">+RIGHT(DEC2HEX(E12,4),2)</f>
-        <v>45</v>
+        <v>8A</v>
       </c>
       <c r="I12" s="50" t="str">
         <f ca="1">+LEFT(DEC2HEX(F12,4),2)</f>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="J12" s="51" t="str">
         <f ca="1">+RIGHT(DEC2HEX(F12,4),2)</f>
-        <v>AB</v>
+        <v>9E</v>
       </c>
       <c r="K12" s="34">
         <v>0</v>
@@ -7172,7 +7172,7 @@
       <c r="L12" s="34">
         <v>0</v>
       </c>
-      <c r="M12" s="385"/>
+      <c r="M12" s="375"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A13" s="425"/>
@@ -7188,11 +7188,11 @@
       </c>
       <c r="E13" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>-994</v>
+        <v>-996</v>
       </c>
       <c r="F13" s="2">
         <f t="shared" ref="F13:F44" ca="1" si="3">+RANDBETWEEN(200,500)</f>
-        <v>392</v>
+        <v>422</v>
       </c>
       <c r="G13" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="H13" s="34" t="str">
         <f ca="1">+RIGHT(DEC2HEX(E13,4),2)</f>
-        <v>1E</v>
+        <v>1C</v>
       </c>
       <c r="I13" s="46" t="str">
         <f ca="1">+LEFT(DEC2HEX(F13,4),2)</f>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="J13" s="47" t="str">
         <f ca="1">+RIGHT(DEC2HEX(F13,4),2)</f>
-        <v>88</v>
+        <v>A6</v>
       </c>
       <c r="K13" s="34">
         <v>0</v>
@@ -7216,7 +7216,7 @@
       <c r="L13" s="34">
         <v>0</v>
       </c>
-      <c r="M13" s="385"/>
+      <c r="M13" s="375"/>
       <c r="O13" s="3"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.4">
@@ -7230,11 +7230,11 @@
       </c>
       <c r="E14" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>-902</v>
+        <v>-996</v>
       </c>
       <c r="F14" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>433</v>
+        <v>237</v>
       </c>
       <c r="G14" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -7242,15 +7242,15 @@
       </c>
       <c r="H14" s="34" t="str">
         <f ca="1">+RIGHT(DEC2HEX(E14,4),2)</f>
-        <v>7A</v>
+        <v>1C</v>
       </c>
       <c r="I14" s="46" t="str">
         <f ca="1">+LEFT(DEC2HEX(F14,4),2)</f>
-        <v>01</v>
+        <v>00</v>
       </c>
       <c r="J14" s="47" t="str">
         <f ca="1">+RIGHT(DEC2HEX(F14,4),2)</f>
-        <v>B1</v>
+        <v>ED</v>
       </c>
       <c r="K14" s="34">
         <v>0</v>
@@ -7258,7 +7258,7 @@
       <c r="L14" s="34">
         <v>0</v>
       </c>
-      <c r="M14" s="385"/>
+      <c r="M14" s="375"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A15" s="425"/>
@@ -7271,11 +7271,11 @@
       </c>
       <c r="E15" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>919</v>
+        <v>1000</v>
       </c>
       <c r="F15" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>409</v>
+        <v>284</v>
       </c>
       <c r="G15" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -7283,7 +7283,7 @@
       </c>
       <c r="H15" s="34" t="str">
         <f ca="1">+RIGHT(DEC2HEX(E15,4),2)</f>
-        <v>97</v>
+        <v>E8</v>
       </c>
       <c r="I15" s="46" t="str">
         <f ca="1">+LEFT(DEC2HEX(F15,4),2)</f>
@@ -7291,7 +7291,7 @@
       </c>
       <c r="J15" s="47" t="str">
         <f ca="1">+RIGHT(DEC2HEX(F15,4),2)</f>
-        <v>99</v>
+        <v>1C</v>
       </c>
       <c r="K15" s="34">
         <v>0</v>
@@ -7299,7 +7299,7 @@
       <c r="L15" s="34">
         <v>0</v>
       </c>
-      <c r="M15" s="385"/>
+      <c r="M15" s="375"/>
       <c r="O15" t="str">
         <f>+MID(O14,7,2)</f>
         <v/>
@@ -7316,11 +7316,11 @@
       </c>
       <c r="E16" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>-921</v>
+        <v>-994</v>
       </c>
       <c r="F16" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>435</v>
+        <v>252</v>
       </c>
       <c r="G16" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -7328,15 +7328,15 @@
       </c>
       <c r="H16" s="34" t="str">
         <f t="shared" ref="H16:H44" ca="1" si="4">+RIGHT(DEC2HEX(E16,4),2)</f>
-        <v>67</v>
+        <v>1E</v>
       </c>
       <c r="I16" s="46" t="str">
         <f t="shared" ref="I16:I44" ca="1" si="5">+LEFT(DEC2HEX(F16,4),2)</f>
-        <v>01</v>
+        <v>00</v>
       </c>
       <c r="J16" s="47" t="str">
         <f t="shared" ref="J16:J44" ca="1" si="6">+RIGHT(DEC2HEX(F16,4),2)</f>
-        <v>B3</v>
+        <v>FC</v>
       </c>
       <c r="K16" s="34">
         <v>0</v>
@@ -7344,7 +7344,7 @@
       <c r="L16" s="34">
         <v>0</v>
       </c>
-      <c r="M16" s="385"/>
+      <c r="M16" s="375"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A17" s="425"/>
@@ -7357,11 +7357,11 @@
       </c>
       <c r="E17" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>903</v>
+        <v>985</v>
       </c>
       <c r="F17" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>256</v>
+        <v>307</v>
       </c>
       <c r="G17" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -7369,7 +7369,7 @@
       </c>
       <c r="H17" s="34" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>87</v>
+        <v>D9</v>
       </c>
       <c r="I17" s="46" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7377,7 +7377,7 @@
       </c>
       <c r="J17" s="47" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>00</v>
+        <v>33</v>
       </c>
       <c r="K17" s="34">
         <v>0</v>
@@ -7385,7 +7385,7 @@
       <c r="L17" s="34">
         <v>0</v>
       </c>
-      <c r="M17" s="385"/>
+      <c r="M17" s="375"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A18" s="425"/>
@@ -7398,11 +7398,11 @@
       </c>
       <c r="E18" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>952</v>
+        <v>915</v>
       </c>
       <c r="F18" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>204</v>
+        <v>265</v>
       </c>
       <c r="G18" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -7410,15 +7410,15 @@
       </c>
       <c r="H18" s="34" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>B8</v>
+        <v>93</v>
       </c>
       <c r="I18" s="46" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>00</v>
+        <v>01</v>
       </c>
       <c r="J18" s="47" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>CC</v>
+        <v>09</v>
       </c>
       <c r="K18" s="34">
         <v>0</v>
@@ -7426,40 +7426,40 @@
       <c r="L18" s="34">
         <v>0</v>
       </c>
-      <c r="M18" s="385"/>
+      <c r="M18" s="375"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A19" s="425"/>
       <c r="C19" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D19" s="33">
         <v>8</v>
       </c>
       <c r="E19" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>-997</v>
+        <v>951</v>
       </c>
       <c r="F19" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>254</v>
+        <v>412</v>
       </c>
       <c r="G19" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>FC</v>
+        <v>00</v>
       </c>
       <c r="H19" s="34" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>1B</v>
+        <v>B7</v>
       </c>
       <c r="I19" s="46" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>00</v>
+        <v>01</v>
       </c>
       <c r="J19" s="47" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>FE</v>
+        <v>9C</v>
       </c>
       <c r="K19" s="34">
         <v>0</v>
@@ -7467,32 +7467,32 @@
       <c r="L19" s="34">
         <v>0</v>
       </c>
-      <c r="M19" s="385"/>
+      <c r="M19" s="375"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A20" s="425"/>
       <c r="C20" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D20" s="33">
         <v>9</v>
       </c>
       <c r="E20" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>946</v>
+        <v>-949</v>
       </c>
       <c r="F20" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>417</v>
+        <v>373</v>
       </c>
       <c r="G20" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>00</v>
+        <v>FC</v>
       </c>
       <c r="H20" s="34" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>B2</v>
+        <v>4B</v>
       </c>
       <c r="I20" s="46" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7500,7 +7500,7 @@
       </c>
       <c r="J20" s="47" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>A1</v>
+        <v>75</v>
       </c>
       <c r="K20" s="34">
         <v>0</v>
@@ -7508,7 +7508,7 @@
       <c r="L20" s="34">
         <v>0</v>
       </c>
-      <c r="M20" s="385"/>
+      <c r="M20" s="375"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A21" s="425"/>
@@ -7521,11 +7521,11 @@
       </c>
       <c r="E21" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>-912</v>
+        <v>-971</v>
       </c>
       <c r="F21" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="G21" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -7533,7 +7533,7 @@
       </c>
       <c r="H21" s="34" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="I21" s="46" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7541,7 +7541,7 @@
       </c>
       <c r="J21" s="47" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K21" s="34">
         <v>0</v>
@@ -7549,32 +7549,32 @@
       <c r="L21" s="34">
         <v>0</v>
       </c>
-      <c r="M21" s="385"/>
+      <c r="M21" s="375"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A22" s="425"/>
       <c r="C22" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D22" s="33">
         <v>11</v>
       </c>
       <c r="E22" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>-942</v>
+        <v>956</v>
       </c>
       <c r="F22" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>286</v>
+        <v>496</v>
       </c>
       <c r="G22" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>FC</v>
+        <v>00</v>
       </c>
       <c r="H22" s="34" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>52</v>
+        <v>BC</v>
       </c>
       <c r="I22" s="46" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7582,7 +7582,7 @@
       </c>
       <c r="J22" s="47" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>1E</v>
+        <v>F0</v>
       </c>
       <c r="K22" s="34">
         <v>0</v>
@@ -7590,7 +7590,7 @@
       <c r="L22" s="34">
         <v>0</v>
       </c>
-      <c r="M22" s="385"/>
+      <c r="M22" s="375"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A23" s="425"/>
@@ -7603,11 +7603,11 @@
       </c>
       <c r="E23" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>-949</v>
+        <v>-910</v>
       </c>
       <c r="F23" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>359</v>
+        <v>475</v>
       </c>
       <c r="G23" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -7615,7 +7615,7 @@
       </c>
       <c r="H23" s="34" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>4B</v>
+        <v>72</v>
       </c>
       <c r="I23" s="46" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="J23" s="47" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>67</v>
+        <v>DB</v>
       </c>
       <c r="K23" s="34">
         <v>0</v>
@@ -7631,7 +7631,7 @@
       <c r="L23" s="34">
         <v>0</v>
       </c>
-      <c r="M23" s="385"/>
+      <c r="M23" s="375"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A24" s="425"/>
@@ -7644,11 +7644,11 @@
       </c>
       <c r="E24" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>-929</v>
+        <v>-993</v>
       </c>
       <c r="F24" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="G24" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -7656,7 +7656,7 @@
       </c>
       <c r="H24" s="34" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>5F</v>
+        <v>1F</v>
       </c>
       <c r="I24" s="46" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7664,7 +7664,7 @@
       </c>
       <c r="J24" s="47" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>1B</v>
+        <v>31</v>
       </c>
       <c r="K24" s="34">
         <v>0</v>
@@ -7672,32 +7672,32 @@
       <c r="L24" s="34">
         <v>0</v>
       </c>
-      <c r="M24" s="385"/>
+      <c r="M24" s="375"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A25" s="425"/>
       <c r="C25" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D25" s="33">
         <v>14</v>
       </c>
       <c r="E25" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>-983</v>
+        <v>945</v>
       </c>
       <c r="F25" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>440</v>
+        <v>366</v>
       </c>
       <c r="G25" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>FC</v>
+        <v>00</v>
       </c>
       <c r="H25" s="34" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>29</v>
+        <v>B1</v>
       </c>
       <c r="I25" s="46" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="J25" s="47" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>B8</v>
+        <v>6E</v>
       </c>
       <c r="K25" s="34">
         <v>0</v>
@@ -7713,7 +7713,7 @@
       <c r="L25" s="34">
         <v>0</v>
       </c>
-      <c r="M25" s="385"/>
+      <c r="M25" s="375"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A26" s="425"/>
@@ -7726,11 +7726,11 @@
       </c>
       <c r="E26" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>916</v>
+        <v>971</v>
       </c>
       <c r="F26" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>232</v>
+        <v>395</v>
       </c>
       <c r="G26" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -7738,15 +7738,15 @@
       </c>
       <c r="H26" s="34" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>94</v>
+        <v>CB</v>
       </c>
       <c r="I26" s="46" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>00</v>
+        <v>01</v>
       </c>
       <c r="J26" s="47" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>E8</v>
+        <v>8B</v>
       </c>
       <c r="K26" s="34">
         <v>0</v>
@@ -7754,40 +7754,40 @@
       <c r="L26" s="34">
         <v>0</v>
       </c>
-      <c r="M26" s="385"/>
+      <c r="M26" s="375"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A27" s="425"/>
       <c r="C27" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D27" s="33">
         <v>16</v>
       </c>
       <c r="E27" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>972</v>
+        <v>-965</v>
       </c>
       <c r="F27" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>239</v>
+        <v>411</v>
       </c>
       <c r="G27" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>00</v>
+        <v>FC</v>
       </c>
       <c r="H27" s="34" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>CC</v>
+        <v>3B</v>
       </c>
       <c r="I27" s="46" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>00</v>
+        <v>01</v>
       </c>
       <c r="J27" s="47" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>EF</v>
+        <v>9B</v>
       </c>
       <c r="K27" s="34">
         <v>0</v>
@@ -7795,7 +7795,7 @@
       <c r="L27" s="34">
         <v>0</v>
       </c>
-      <c r="M27" s="385"/>
+      <c r="M27" s="375"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A28" s="425"/>
@@ -7808,11 +7808,11 @@
       </c>
       <c r="E28" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>-941</v>
+        <v>-973</v>
       </c>
       <c r="F28" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>252</v>
+        <v>498</v>
       </c>
       <c r="G28" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -7820,15 +7820,15 @@
       </c>
       <c r="H28" s="34" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="I28" s="46" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>00</v>
+        <v>01</v>
       </c>
       <c r="J28" s="47" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>FC</v>
+        <v>F2</v>
       </c>
       <c r="K28" s="34">
         <v>0</v>
@@ -7836,7 +7836,7 @@
       <c r="L28" s="34">
         <v>0</v>
       </c>
-      <c r="M28" s="385"/>
+      <c r="M28" s="375"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A29" s="425"/>
@@ -7849,11 +7849,11 @@
       </c>
       <c r="E29" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>-913</v>
+        <v>-922</v>
       </c>
       <c r="F29" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>361</v>
+        <v>436</v>
       </c>
       <c r="G29" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -7861,7 +7861,7 @@
       </c>
       <c r="H29" s="34" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>6F</v>
+        <v>66</v>
       </c>
       <c r="I29" s="46" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="J29" s="47" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>69</v>
+        <v>B4</v>
       </c>
       <c r="K29" s="34">
         <v>0</v>
@@ -7877,32 +7877,32 @@
       <c r="L29" s="34">
         <v>0</v>
       </c>
-      <c r="M29" s="385"/>
+      <c r="M29" s="375"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A30" s="425"/>
       <c r="C30" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D30" s="33">
         <v>19</v>
       </c>
       <c r="E30" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>925</v>
+        <v>-994</v>
       </c>
       <c r="F30" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>336</v>
+        <v>440</v>
       </c>
       <c r="G30" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>00</v>
+        <v>FC</v>
       </c>
       <c r="H30" s="34" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>9D</v>
+        <v>1E</v>
       </c>
       <c r="I30" s="46" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7910,7 +7910,7 @@
       </c>
       <c r="J30" s="47" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>50</v>
+        <v>B8</v>
       </c>
       <c r="K30" s="34">
         <v>0</v>
@@ -7918,32 +7918,32 @@
       <c r="L30" s="34">
         <v>0</v>
       </c>
-      <c r="M30" s="385"/>
+      <c r="M30" s="375"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A31" s="425"/>
       <c r="C31" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D31" s="33">
         <v>20</v>
       </c>
       <c r="E31" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>911</v>
+        <v>-907</v>
       </c>
       <c r="F31" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>292</v>
+        <v>376</v>
       </c>
       <c r="G31" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>00</v>
+        <v>FC</v>
       </c>
       <c r="H31" s="34" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>8F</v>
+        <v>75</v>
       </c>
       <c r="I31" s="46" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="J31" s="47" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="K31" s="34">
         <v>0</v>
@@ -7959,7 +7959,7 @@
       <c r="L31" s="34">
         <v>0</v>
       </c>
-      <c r="M31" s="385"/>
+      <c r="M31" s="375"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A32" s="425"/>
@@ -7972,11 +7972,11 @@
       </c>
       <c r="E32" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>-953</v>
+        <v>-904</v>
       </c>
       <c r="F32" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>286</v>
+        <v>488</v>
       </c>
       <c r="G32" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="H32" s="34" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="I32" s="46" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="J32" s="47" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>1E</v>
+        <v>E8</v>
       </c>
       <c r="K32" s="34">
         <v>0</v>
@@ -8000,40 +8000,40 @@
       <c r="L32" s="34">
         <v>0</v>
       </c>
-      <c r="M32" s="385"/>
+      <c r="M32" s="375"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A33" s="425"/>
       <c r="C33" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D33" s="33">
         <v>22</v>
       </c>
       <c r="E33" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>-948</v>
+        <v>955</v>
       </c>
       <c r="F33" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>241</v>
+        <v>304</v>
       </c>
       <c r="G33" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>FC</v>
+        <v>00</v>
       </c>
       <c r="H33" s="34" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>4C</v>
+        <v>BB</v>
       </c>
       <c r="I33" s="46" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>00</v>
+        <v>01</v>
       </c>
       <c r="J33" s="47" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>F1</v>
+        <v>30</v>
       </c>
       <c r="K33" s="34">
         <v>0</v>
@@ -8041,40 +8041,40 @@
       <c r="L33" s="34">
         <v>0</v>
       </c>
-      <c r="M33" s="385"/>
+      <c r="M33" s="375"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A34" s="425"/>
       <c r="C34" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D34" s="33">
         <v>23</v>
       </c>
       <c r="E34" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>980</v>
+        <v>-978</v>
       </c>
       <c r="F34" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>258</v>
+        <v>209</v>
       </c>
       <c r="G34" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>00</v>
+        <v>FC</v>
       </c>
       <c r="H34" s="34" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>D4</v>
+        <v>2E</v>
       </c>
       <c r="I34" s="46" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>01</v>
+        <v>00</v>
       </c>
       <c r="J34" s="47" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>02</v>
+        <v>D1</v>
       </c>
       <c r="K34" s="34">
         <v>0</v>
@@ -8082,40 +8082,40 @@
       <c r="L34" s="34">
         <v>0</v>
       </c>
-      <c r="M34" s="385"/>
+      <c r="M34" s="375"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A35" s="425"/>
       <c r="C35" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D35" s="33">
         <v>24</v>
       </c>
       <c r="E35" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>-904</v>
+        <v>993</v>
       </c>
       <c r="F35" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>223</v>
+        <v>444</v>
       </c>
       <c r="G35" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>FC</v>
+        <v>00</v>
       </c>
       <c r="H35" s="34" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>78</v>
+        <v>E1</v>
       </c>
       <c r="I35" s="46" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>00</v>
+        <v>01</v>
       </c>
       <c r="J35" s="47" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>DF</v>
+        <v>BC</v>
       </c>
       <c r="K35" s="34">
         <v>0</v>
@@ -8123,7 +8123,7 @@
       <c r="L35" s="34">
         <v>0</v>
       </c>
-      <c r="M35" s="385"/>
+      <c r="M35" s="375"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A36" s="425"/>
@@ -8136,11 +8136,11 @@
       </c>
       <c r="E36" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>-996</v>
+        <v>-979</v>
       </c>
       <c r="F36" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="G36" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -8148,7 +8148,7 @@
       </c>
       <c r="H36" s="34" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>1C</v>
+        <v>2D</v>
       </c>
       <c r="I36" s="46" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="J36" s="47" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>AA</v>
+        <v>B7</v>
       </c>
       <c r="K36" s="34">
         <v>0</v>
@@ -8164,32 +8164,32 @@
       <c r="L36" s="34">
         <v>0</v>
       </c>
-      <c r="M36" s="385"/>
+      <c r="M36" s="375"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A37" s="425"/>
       <c r="C37" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D37" s="33">
         <v>26</v>
       </c>
       <c r="E37" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>992</v>
+        <v>-956</v>
       </c>
       <c r="F37" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>444</v>
+        <v>386</v>
       </c>
       <c r="G37" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>00</v>
+        <v>FC</v>
       </c>
       <c r="H37" s="34" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>E0</v>
+        <v>44</v>
       </c>
       <c r="I37" s="46" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8197,7 +8197,7 @@
       </c>
       <c r="J37" s="47" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>BC</v>
+        <v>82</v>
       </c>
       <c r="K37" s="34">
         <v>0</v>
@@ -8205,7 +8205,7 @@
       <c r="L37" s="34">
         <v>0</v>
       </c>
-      <c r="M37" s="385"/>
+      <c r="M37" s="375"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A38" s="425"/>
@@ -8218,11 +8218,11 @@
       </c>
       <c r="E38" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>-942</v>
+        <v>-996</v>
       </c>
       <c r="F38" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>416</v>
+        <v>486</v>
       </c>
       <c r="G38" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -8230,7 +8230,7 @@
       </c>
       <c r="H38" s="34" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>52</v>
+        <v>1C</v>
       </c>
       <c r="I38" s="46" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8238,7 +8238,7 @@
       </c>
       <c r="J38" s="47" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>A0</v>
+        <v>E6</v>
       </c>
       <c r="K38" s="34">
         <v>0</v>
@@ -8246,7 +8246,7 @@
       <c r="L38" s="34">
         <v>0</v>
       </c>
-      <c r="M38" s="385"/>
+      <c r="M38" s="375"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A39" s="425"/>
@@ -8259,11 +8259,11 @@
       </c>
       <c r="E39" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>-905</v>
+        <v>-929</v>
       </c>
       <c r="F39" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>244</v>
+        <v>285</v>
       </c>
       <c r="G39" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -8271,15 +8271,15 @@
       </c>
       <c r="H39" s="34" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>77</v>
+        <v>5F</v>
       </c>
       <c r="I39" s="46" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>00</v>
+        <v>01</v>
       </c>
       <c r="J39" s="47" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>F4</v>
+        <v>1D</v>
       </c>
       <c r="K39" s="34">
         <v>0</v>
@@ -8287,7 +8287,7 @@
       <c r="L39" s="34">
         <v>0</v>
       </c>
-      <c r="M39" s="385"/>
+      <c r="M39" s="375"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A40" s="425"/>
@@ -8300,11 +8300,11 @@
       </c>
       <c r="E40" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>975</v>
+        <v>926</v>
       </c>
       <c r="F40" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>236</v>
+        <v>325</v>
       </c>
       <c r="G40" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -8312,15 +8312,15 @@
       </c>
       <c r="H40" s="34" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>CF</v>
+        <v>9E</v>
       </c>
       <c r="I40" s="46" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>00</v>
+        <v>01</v>
       </c>
       <c r="J40" s="47" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>EC</v>
+        <v>45</v>
       </c>
       <c r="K40" s="34">
         <v>0</v>
@@ -8328,7 +8328,7 @@
       <c r="L40" s="34">
         <v>0</v>
       </c>
-      <c r="M40" s="385"/>
+      <c r="M40" s="375"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A41" s="425"/>
@@ -8341,11 +8341,11 @@
       </c>
       <c r="E41" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>933</v>
+        <v>954</v>
       </c>
       <c r="F41" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>437</v>
+        <v>271</v>
       </c>
       <c r="G41" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="H41" s="34" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>A5</v>
+        <v>BA</v>
       </c>
       <c r="I41" s="46" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8361,7 +8361,7 @@
       </c>
       <c r="J41" s="47" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>B5</v>
+        <v>0F</v>
       </c>
       <c r="K41" s="34">
         <v>0</v>
@@ -8369,7 +8369,7 @@
       <c r="L41" s="34">
         <v>0</v>
       </c>
-      <c r="M41" s="385"/>
+      <c r="M41" s="375"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A42" s="425"/>
@@ -8382,11 +8382,11 @@
       </c>
       <c r="E42" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>-948</v>
+        <v>-905</v>
       </c>
       <c r="F42" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>492</v>
+        <v>286</v>
       </c>
       <c r="G42" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -8394,7 +8394,7 @@
       </c>
       <c r="H42" s="34" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>4C</v>
+        <v>77</v>
       </c>
       <c r="I42" s="46" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="J42" s="47" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>EC</v>
+        <v>1E</v>
       </c>
       <c r="K42" s="34">
         <v>0</v>
@@ -8410,40 +8410,40 @@
       <c r="L42" s="34">
         <v>0</v>
       </c>
-      <c r="M42" s="385"/>
+      <c r="M42" s="375"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A43" s="425"/>
       <c r="C43" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D43" s="33">
         <v>32</v>
       </c>
       <c r="E43" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>916</v>
+        <v>-933</v>
       </c>
       <c r="F43" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>454</v>
+        <v>215</v>
       </c>
       <c r="G43" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>00</v>
+        <v>FC</v>
       </c>
       <c r="H43" s="34" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>94</v>
+        <v>5B</v>
       </c>
       <c r="I43" s="46" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>01</v>
+        <v>00</v>
       </c>
       <c r="J43" s="47" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>C6</v>
+        <v>D7</v>
       </c>
       <c r="K43" s="34">
         <v>0</v>
@@ -8451,32 +8451,32 @@
       <c r="L43" s="34">
         <v>0</v>
       </c>
-      <c r="M43" s="385"/>
+      <c r="M43" s="375"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A44" s="425"/>
       <c r="C44" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D44" s="33">
         <v>33</v>
       </c>
       <c r="E44" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>-997</v>
+        <v>933</v>
       </c>
       <c r="F44" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>291</v>
+        <v>429</v>
       </c>
       <c r="G44" s="34" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>FC</v>
+        <v>00</v>
       </c>
       <c r="H44" s="34" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>1B</v>
+        <v>A5</v>
       </c>
       <c r="I44" s="46" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="J44" s="47" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>23</v>
+        <v>AD</v>
       </c>
       <c r="K44" s="34">
         <v>0</v>
@@ -8492,7 +8492,7 @@
       <c r="L44" s="34">
         <v>0</v>
       </c>
-      <c r="M44" s="385"/>
+      <c r="M44" s="375"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A45" s="425"/>
@@ -8508,7 +8508,7 @@
       <c r="J45" s="49"/>
       <c r="K45" s="34"/>
       <c r="L45" s="42"/>
-      <c r="M45" s="386"/>
+      <c r="M45" s="376"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A46" s="10"/>
@@ -8736,7 +8736,7 @@
         <v>2</v>
       </c>
       <c r="I12" s="34"/>
-      <c r="J12" s="385"/>
+      <c r="J12" s="375"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13" s="425"/>
@@ -8760,7 +8760,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="34"/>
-      <c r="J13" s="385"/>
+      <c r="J13" s="375"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14" s="425"/>
@@ -8781,7 +8781,7 @@
         <v>4</v>
       </c>
       <c r="I14" s="34"/>
-      <c r="J14" s="385"/>
+      <c r="J14" s="375"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15" s="425"/>
@@ -8792,7 +8792,7 @@
       <c r="G15" s="47"/>
       <c r="H15" s="34"/>
       <c r="I15" s="34"/>
-      <c r="J15" s="385"/>
+      <c r="J15" s="375"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16" s="425"/>
@@ -8803,7 +8803,7 @@
       <c r="G16" s="47"/>
       <c r="H16" s="34"/>
       <c r="I16" s="34"/>
-      <c r="J16" s="385"/>
+      <c r="J16" s="375"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A17" s="425"/>
@@ -8814,7 +8814,7 @@
       <c r="G17" s="47"/>
       <c r="H17" s="34"/>
       <c r="I17" s="34"/>
-      <c r="J17" s="385"/>
+      <c r="J17" s="375"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A18" s="425"/>
@@ -8825,7 +8825,7 @@
       <c r="G18" s="47"/>
       <c r="H18" s="34"/>
       <c r="I18" s="34"/>
-      <c r="J18" s="385"/>
+      <c r="J18" s="375"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19" s="425"/>
@@ -8836,7 +8836,7 @@
       <c r="G19" s="47"/>
       <c r="H19" s="34"/>
       <c r="I19" s="34"/>
-      <c r="J19" s="385"/>
+      <c r="J19" s="375"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.4">
       <c r="C20" s="33"/>
@@ -8846,7 +8846,7 @@
       <c r="G20" s="49"/>
       <c r="H20" s="34"/>
       <c r="I20" s="42"/>
-      <c r="J20" s="386"/>
+      <c r="J20" s="376"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A21" s="10"/>
@@ -9107,7 +9107,7 @@
       <c r="L12" s="34">
         <v>0</v>
       </c>
-      <c r="M12" s="385"/>
+      <c r="M12" s="375"/>
       <c r="O12" s="2"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.4">
@@ -9151,7 +9151,7 @@
       <c r="L13" s="34">
         <v>0</v>
       </c>
-      <c r="M13" s="385"/>
+      <c r="M13" s="375"/>
       <c r="O13" s="2"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.4">
@@ -9192,14 +9192,14 @@
       <c r="L14" s="34">
         <v>0</v>
       </c>
-      <c r="M14" s="385"/>
+      <c r="M14" s="375"/>
       <c r="O14" s="2"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A15" s="425"/>
       <c r="C15" s="33">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D15" s="33">
         <v>4</v>
@@ -9233,7 +9233,7 @@
       <c r="L15" s="34">
         <v>0</v>
       </c>
-      <c r="M15" s="385"/>
+      <c r="M15" s="375"/>
       <c r="O15" s="2"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.4">
@@ -9274,14 +9274,14 @@
       <c r="L16" s="34">
         <v>0</v>
       </c>
-      <c r="M16" s="385"/>
+      <c r="M16" s="375"/>
       <c r="O16" s="2"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A17" s="425"/>
       <c r="C17" s="33">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D17" s="33">
         <v>6</v>
@@ -9315,14 +9315,14 @@
       <c r="L17" s="34">
         <v>0</v>
       </c>
-      <c r="M17" s="385"/>
+      <c r="M17" s="375"/>
       <c r="O17" s="2"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A18" s="425"/>
       <c r="C18" s="33">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D18" s="33">
         <v>7</v>
@@ -9356,7 +9356,7 @@
       <c r="L18" s="34">
         <v>0</v>
       </c>
-      <c r="M18" s="385"/>
+      <c r="M18" s="375"/>
       <c r="O18" s="2"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.4">
@@ -9397,14 +9397,14 @@
       <c r="L19" s="34">
         <v>0</v>
       </c>
-      <c r="M19" s="385"/>
+      <c r="M19" s="375"/>
       <c r="O19" s="2"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A20" s="425"/>
       <c r="C20" s="33">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D20" s="33">
         <v>9</v>
@@ -9438,7 +9438,7 @@
       <c r="L20" s="34">
         <v>0</v>
       </c>
-      <c r="M20" s="385"/>
+      <c r="M20" s="375"/>
       <c r="O20" s="2"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.4">
@@ -9479,14 +9479,14 @@
       <c r="L21" s="34">
         <v>0</v>
       </c>
-      <c r="M21" s="385"/>
+      <c r="M21" s="375"/>
       <c r="O21" s="2"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A22" s="425"/>
       <c r="C22" s="33">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D22" s="33"/>
       <c r="E22" s="2"/>
@@ -9496,13 +9496,13 @@
       <c r="J22" s="34"/>
       <c r="K22" s="34"/>
       <c r="L22" s="34"/>
-      <c r="M22" s="385"/>
+      <c r="M22" s="375"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A23" s="425"/>
       <c r="C23" s="33">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D23" s="33"/>
       <c r="E23" s="2"/>
@@ -9512,13 +9512,13 @@
       <c r="J23" s="34"/>
       <c r="K23" s="34"/>
       <c r="L23" s="34"/>
-      <c r="M23" s="385"/>
+      <c r="M23" s="375"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A24" s="425"/>
       <c r="C24" s="33">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D24" s="33"/>
       <c r="E24" s="2"/>
@@ -9528,13 +9528,13 @@
       <c r="J24" s="34"/>
       <c r="K24" s="34"/>
       <c r="L24" s="34"/>
-      <c r="M24" s="385"/>
+      <c r="M24" s="375"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A25" s="425"/>
       <c r="C25" s="33">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D25" s="33"/>
       <c r="E25" s="2"/>
@@ -9544,7 +9544,7 @@
       <c r="J25" s="34"/>
       <c r="K25" s="34"/>
       <c r="L25" s="34"/>
-      <c r="M25" s="385"/>
+      <c r="M25" s="375"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A26" s="425"/>
@@ -9560,13 +9560,13 @@
       <c r="J26" s="34"/>
       <c r="K26" s="34"/>
       <c r="L26" s="34"/>
-      <c r="M26" s="385"/>
+      <c r="M26" s="375"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A27" s="425"/>
       <c r="C27" s="33">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D27" s="33"/>
       <c r="E27" s="2"/>
@@ -9576,7 +9576,7 @@
       <c r="J27" s="34"/>
       <c r="K27" s="34"/>
       <c r="L27" s="34"/>
-      <c r="M27" s="385"/>
+      <c r="M27" s="375"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A28" s="425"/>
@@ -9592,13 +9592,13 @@
       <c r="J28" s="34"/>
       <c r="K28" s="34"/>
       <c r="L28" s="34"/>
-      <c r="M28" s="385"/>
+      <c r="M28" s="375"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A29" s="425"/>
       <c r="C29" s="33">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D29" s="33"/>
       <c r="E29" s="2"/>
@@ -9608,7 +9608,7 @@
       <c r="J29" s="34"/>
       <c r="K29" s="34"/>
       <c r="L29" s="34"/>
-      <c r="M29" s="385"/>
+      <c r="M29" s="375"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A30" s="425"/>
@@ -9624,7 +9624,7 @@
       <c r="J30" s="34"/>
       <c r="K30" s="34"/>
       <c r="L30" s="34"/>
-      <c r="M30" s="385"/>
+      <c r="M30" s="375"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A31" s="425"/>
@@ -9640,7 +9640,7 @@
       <c r="J31" s="34"/>
       <c r="K31" s="34"/>
       <c r="L31" s="34"/>
-      <c r="M31" s="385"/>
+      <c r="M31" s="375"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A32" s="425"/>
@@ -9656,7 +9656,7 @@
       <c r="J32" s="34"/>
       <c r="K32" s="34"/>
       <c r="L32" s="34"/>
-      <c r="M32" s="385"/>
+      <c r="M32" s="375"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A33" s="425"/>
@@ -9672,7 +9672,7 @@
       <c r="J33" s="34"/>
       <c r="K33" s="34"/>
       <c r="L33" s="34"/>
-      <c r="M33" s="385"/>
+      <c r="M33" s="375"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A34" s="425"/>
@@ -9688,7 +9688,7 @@
       <c r="J34" s="34"/>
       <c r="K34" s="34"/>
       <c r="L34" s="34"/>
-      <c r="M34" s="385"/>
+      <c r="M34" s="375"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A35" s="425"/>
@@ -9704,7 +9704,7 @@
       <c r="J35" s="34"/>
       <c r="K35" s="34"/>
       <c r="L35" s="34"/>
-      <c r="M35" s="385"/>
+      <c r="M35" s="375"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A36" s="425"/>
@@ -9720,13 +9720,13 @@
       <c r="J36" s="34"/>
       <c r="K36" s="34"/>
       <c r="L36" s="34"/>
-      <c r="M36" s="385"/>
+      <c r="M36" s="375"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A37" s="425"/>
       <c r="C37" s="33">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D37" s="33"/>
       <c r="E37" s="2"/>
@@ -9736,7 +9736,7 @@
       <c r="J37" s="34"/>
       <c r="K37" s="34"/>
       <c r="L37" s="34"/>
-      <c r="M37" s="385"/>
+      <c r="M37" s="375"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A38" s="425"/>
@@ -9752,7 +9752,7 @@
       <c r="J38" s="34"/>
       <c r="K38" s="34"/>
       <c r="L38" s="34"/>
-      <c r="M38" s="385"/>
+      <c r="M38" s="375"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A39" s="425"/>
@@ -9768,7 +9768,7 @@
       <c r="J39" s="34"/>
       <c r="K39" s="34"/>
       <c r="L39" s="34"/>
-      <c r="M39" s="385"/>
+      <c r="M39" s="375"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A40" s="425"/>
@@ -9784,13 +9784,13 @@
       <c r="J40" s="34"/>
       <c r="K40" s="34"/>
       <c r="L40" s="34"/>
-      <c r="M40" s="385"/>
+      <c r="M40" s="375"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A41" s="425"/>
       <c r="C41" s="33">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D41" s="33"/>
       <c r="E41" s="2"/>
@@ -9800,13 +9800,13 @@
       <c r="J41" s="34"/>
       <c r="K41" s="34"/>
       <c r="L41" s="34"/>
-      <c r="M41" s="385"/>
+      <c r="M41" s="375"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A42" s="425"/>
       <c r="C42" s="33">
         <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D42" s="33"/>
       <c r="E42" s="2"/>
@@ -9816,13 +9816,13 @@
       <c r="J42" s="34"/>
       <c r="K42" s="34"/>
       <c r="L42" s="34"/>
-      <c r="M42" s="385"/>
+      <c r="M42" s="375"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A43" s="425"/>
       <c r="C43" s="33">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D43" s="33"/>
       <c r="E43" s="2"/>
@@ -9832,7 +9832,7 @@
       <c r="J43" s="34"/>
       <c r="K43" s="34"/>
       <c r="L43" s="34"/>
-      <c r="M43" s="385"/>
+      <c r="M43" s="375"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A44" s="425"/>
@@ -9848,7 +9848,7 @@
       <c r="J44" s="34"/>
       <c r="K44" s="34"/>
       <c r="L44" s="34"/>
-      <c r="M44" s="385"/>
+      <c r="M44" s="375"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A45" s="425"/>
@@ -9864,7 +9864,7 @@
       <c r="J45" s="34"/>
       <c r="K45" s="34"/>
       <c r="L45" s="42"/>
-      <c r="M45" s="386"/>
+      <c r="M45" s="376"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A46" s="10"/>
@@ -10136,10 +10136,10 @@
       <c r="E3" s="57"/>
       <c r="F3" s="57"/>
       <c r="G3" s="57"/>
-      <c r="H3" s="328" t="s">
+      <c r="H3" s="353" t="s">
         <v>130</v>
       </c>
-      <c r="I3" s="329"/>
+      <c r="I3" s="354"/>
       <c r="J3" s="253"/>
     </row>
     <row r="4" spans="1:10" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -10162,17 +10162,17 @@
       <c r="G4" s="62" t="s">
         <v>132</v>
       </c>
-      <c r="H4" s="330" t="s">
+      <c r="H4" s="355" t="s">
         <v>114</v>
       </c>
-      <c r="I4" s="331"/>
+      <c r="I4" s="356"/>
       <c r="J4" s="254" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="91.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="342"/>
-      <c r="B5" s="349" t="s">
+      <c r="A5" s="340"/>
+      <c r="B5" s="332" t="s">
         <v>133</v>
       </c>
       <c r="C5" s="230" t="s">
@@ -10197,22 +10197,22 @@
       <c r="J5" s="255"/>
     </row>
     <row r="6" spans="1:10" ht="62.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="343"/>
-      <c r="B6" s="350"/>
-      <c r="C6" s="332" t="s">
+      <c r="A6" s="341"/>
+      <c r="B6" s="333"/>
+      <c r="C6" s="346" t="s">
         <v>138</v>
       </c>
-      <c r="D6" s="333"/>
-      <c r="E6" s="333"/>
-      <c r="F6" s="333"/>
-      <c r="G6" s="333"/>
-      <c r="H6" s="333"/>
-      <c r="I6" s="333"/>
-      <c r="J6" s="334"/>
+      <c r="D6" s="347"/>
+      <c r="E6" s="347"/>
+      <c r="F6" s="347"/>
+      <c r="G6" s="347"/>
+      <c r="H6" s="347"/>
+      <c r="I6" s="347"/>
+      <c r="J6" s="348"/>
     </row>
     <row r="7" spans="1:10" ht="94.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="344"/>
-      <c r="B7" s="351" t="s">
+      <c r="A7" s="328"/>
+      <c r="B7" s="334" t="s">
         <v>139</v>
       </c>
       <c r="C7" s="234" t="s">
@@ -10239,22 +10239,22 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="102" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="345"/>
-      <c r="B8" s="352"/>
-      <c r="C8" s="335" t="s">
+      <c r="A8" s="329"/>
+      <c r="B8" s="335"/>
+      <c r="C8" s="343" t="s">
         <v>144</v>
       </c>
-      <c r="D8" s="336"/>
-      <c r="E8" s="336"/>
-      <c r="F8" s="336"/>
-      <c r="G8" s="336"/>
-      <c r="H8" s="336"/>
-      <c r="I8" s="336"/>
-      <c r="J8" s="337"/>
+      <c r="D8" s="344"/>
+      <c r="E8" s="344"/>
+      <c r="F8" s="344"/>
+      <c r="G8" s="344"/>
+      <c r="H8" s="344"/>
+      <c r="I8" s="344"/>
+      <c r="J8" s="345"/>
     </row>
     <row r="9" spans="1:10" ht="129.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="344"/>
-      <c r="B9" s="353" t="s">
+      <c r="A9" s="328"/>
+      <c r="B9" s="336" t="s">
         <v>145</v>
       </c>
       <c r="C9" s="235" t="s">
@@ -10283,22 +10283,22 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="123.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="345"/>
-      <c r="B10" s="354"/>
-      <c r="C10" s="335" t="s">
+      <c r="A10" s="329"/>
+      <c r="B10" s="337"/>
+      <c r="C10" s="343" t="s">
         <v>151</v>
       </c>
-      <c r="D10" s="336"/>
-      <c r="E10" s="336"/>
-      <c r="F10" s="336"/>
-      <c r="G10" s="336"/>
-      <c r="H10" s="336"/>
-      <c r="I10" s="336"/>
-      <c r="J10" s="337"/>
+      <c r="D10" s="344"/>
+      <c r="E10" s="344"/>
+      <c r="F10" s="344"/>
+      <c r="G10" s="344"/>
+      <c r="H10" s="344"/>
+      <c r="I10" s="344"/>
+      <c r="J10" s="345"/>
     </row>
     <row r="11" spans="1:10" ht="116.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="344"/>
-      <c r="B11" s="351" t="s">
+      <c r="A11" s="328"/>
+      <c r="B11" s="334" t="s">
         <v>152</v>
       </c>
       <c r="C11" s="238" t="s">
@@ -10327,22 +10327,22 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="69" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="345"/>
-      <c r="B12" s="352"/>
-      <c r="C12" s="335" t="s">
+      <c r="A12" s="329"/>
+      <c r="B12" s="335"/>
+      <c r="C12" s="343" t="s">
         <v>157</v>
       </c>
-      <c r="D12" s="336"/>
-      <c r="E12" s="336"/>
-      <c r="F12" s="336"/>
-      <c r="G12" s="336"/>
-      <c r="H12" s="336"/>
-      <c r="I12" s="336"/>
-      <c r="J12" s="337"/>
+      <c r="D12" s="344"/>
+      <c r="E12" s="344"/>
+      <c r="F12" s="344"/>
+      <c r="G12" s="344"/>
+      <c r="H12" s="344"/>
+      <c r="I12" s="344"/>
+      <c r="J12" s="345"/>
     </row>
     <row r="13" spans="1:10" ht="118.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="346"/>
-      <c r="B13" s="355" t="s">
+      <c r="A13" s="342"/>
+      <c r="B13" s="338" t="s">
         <v>158</v>
       </c>
       <c r="C13" s="241" t="s">
@@ -10369,22 +10369,22 @@
       </c>
     </row>
     <row r="14" spans="1:10" ht="66.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="346"/>
-      <c r="B14" s="350"/>
-      <c r="C14" s="332" t="s">
+      <c r="A14" s="342"/>
+      <c r="B14" s="333"/>
+      <c r="C14" s="346" t="s">
         <v>164</v>
       </c>
-      <c r="D14" s="333"/>
-      <c r="E14" s="333"/>
-      <c r="F14" s="333"/>
-      <c r="G14" s="333"/>
-      <c r="H14" s="333"/>
-      <c r="I14" s="333"/>
-      <c r="J14" s="334"/>
+      <c r="D14" s="347"/>
+      <c r="E14" s="347"/>
+      <c r="F14" s="347"/>
+      <c r="G14" s="347"/>
+      <c r="H14" s="347"/>
+      <c r="I14" s="347"/>
+      <c r="J14" s="348"/>
     </row>
     <row r="15" spans="1:10" ht="127.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="344"/>
-      <c r="B15" s="351" t="s">
+      <c r="A15" s="328"/>
+      <c r="B15" s="334" t="s">
         <v>165</v>
       </c>
       <c r="C15" s="234" t="s">
@@ -10409,18 +10409,18 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="345"/>
-      <c r="B16" s="352"/>
-      <c r="C16" s="338" t="s">
+      <c r="A16" s="329"/>
+      <c r="B16" s="335"/>
+      <c r="C16" s="349" t="s">
         <v>170</v>
       </c>
-      <c r="D16" s="336"/>
-      <c r="E16" s="336"/>
-      <c r="F16" s="336"/>
-      <c r="G16" s="336"/>
-      <c r="H16" s="336"/>
-      <c r="I16" s="336"/>
-      <c r="J16" s="337"/>
+      <c r="D16" s="344"/>
+      <c r="E16" s="344"/>
+      <c r="F16" s="344"/>
+      <c r="G16" s="344"/>
+      <c r="H16" s="344"/>
+      <c r="I16" s="344"/>
+      <c r="J16" s="345"/>
     </row>
     <row r="17" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="98" t="s">
@@ -10448,8 +10448,8 @@
       <c r="J17" s="259"/>
     </row>
     <row r="18" spans="1:10" ht="69" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="344"/>
-      <c r="B18" s="351" t="s">
+      <c r="A18" s="328"/>
+      <c r="B18" s="334" t="s">
         <v>41</v>
       </c>
       <c r="C18" s="234" t="s">
@@ -10476,22 +10476,22 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="345"/>
-      <c r="B19" s="352"/>
-      <c r="C19" s="335" t="s">
+      <c r="A19" s="329"/>
+      <c r="B19" s="335"/>
+      <c r="C19" s="343" t="s">
         <v>178</v>
       </c>
-      <c r="D19" s="336"/>
-      <c r="E19" s="336"/>
-      <c r="F19" s="336"/>
-      <c r="G19" s="336"/>
-      <c r="H19" s="336"/>
-      <c r="I19" s="336"/>
-      <c r="J19" s="337"/>
+      <c r="D19" s="344"/>
+      <c r="E19" s="344"/>
+      <c r="F19" s="344"/>
+      <c r="G19" s="344"/>
+      <c r="H19" s="344"/>
+      <c r="I19" s="344"/>
+      <c r="J19" s="345"/>
     </row>
     <row r="20" spans="1:10" s="21" customFormat="1" ht="211.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="347"/>
-      <c r="B20" s="351" t="s">
+      <c r="A20" s="330"/>
+      <c r="B20" s="334" t="s">
         <v>15</v>
       </c>
       <c r="C20" s="241" t="s">
@@ -10516,18 +10516,18 @@
       </c>
     </row>
     <row r="21" spans="1:10" s="21" customFormat="1" ht="144" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="348"/>
-      <c r="B21" s="356"/>
-      <c r="C21" s="339" t="s">
+      <c r="A21" s="331"/>
+      <c r="B21" s="339"/>
+      <c r="C21" s="350" t="s">
         <v>181</v>
       </c>
-      <c r="D21" s="340"/>
-      <c r="E21" s="340"/>
-      <c r="F21" s="340"/>
-      <c r="G21" s="340"/>
-      <c r="H21" s="340"/>
-      <c r="I21" s="340"/>
-      <c r="J21" s="341"/>
+      <c r="D21" s="351"/>
+      <c r="E21" s="351"/>
+      <c r="F21" s="351"/>
+      <c r="G21" s="351"/>
+      <c r="H21" s="351"/>
+      <c r="I21" s="351"/>
+      <c r="J21" s="352"/>
     </row>
     <row r="22" spans="1:10" s="181" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="246"/>
@@ -10586,6 +10586,16 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="C6:J6"/>
+    <mergeCell ref="C8:J8"/>
+    <mergeCell ref="C10:J10"/>
+    <mergeCell ref="C12:J12"/>
+    <mergeCell ref="C14:J14"/>
+    <mergeCell ref="C16:J16"/>
+    <mergeCell ref="C19:J19"/>
+    <mergeCell ref="C21:J21"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A20:A21"/>
@@ -10602,16 +10612,6 @@
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="A13:A14"/>
-    <mergeCell ref="C12:J12"/>
-    <mergeCell ref="C14:J14"/>
-    <mergeCell ref="C16:J16"/>
-    <mergeCell ref="C19:J19"/>
-    <mergeCell ref="C21:J21"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="C6:J6"/>
-    <mergeCell ref="C8:J8"/>
-    <mergeCell ref="C10:J10"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10737,7 +10737,7 @@
       <c r="K5" s="221"/>
     </row>
     <row r="6" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="345"/>
+      <c r="A6" s="329"/>
       <c r="B6" s="323"/>
       <c r="C6" s="357" t="s">
         <v>194</v>
@@ -10902,10 +10902,10 @@
       <c r="E3" s="57"/>
       <c r="F3" s="57"/>
       <c r="G3" s="57"/>
-      <c r="H3" s="328" t="s">
+      <c r="H3" s="353" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="329"/>
+      <c r="I3" s="354"/>
       <c r="J3" s="69"/>
     </row>
     <row r="4" spans="1:10" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -10928,10 +10928,10 @@
       <c r="G4" s="62" t="s">
         <v>205</v>
       </c>
-      <c r="H4" s="330" t="s">
+      <c r="H4" s="355" t="s">
         <v>114</v>
       </c>
-      <c r="I4" s="331"/>
+      <c r="I4" s="356"/>
       <c r="J4" s="70" t="s">
         <v>115</v>
       </c>
@@ -11039,8 +11039,8 @@
       <c r="J8" s="196"/>
     </row>
     <row r="9" spans="1:10" s="21" customFormat="1" ht="73.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="347"/>
-      <c r="B9" s="351" t="s">
+      <c r="A9" s="330"/>
+      <c r="B9" s="334" t="s">
         <v>221</v>
       </c>
       <c r="C9" s="87" t="s">
@@ -11066,8 +11066,8 @@
     </row>
     <row r="10" spans="1:10" s="21" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="326"/>
-      <c r="B10" s="352"/>
-      <c r="C10" s="364" t="s">
+      <c r="B10" s="335"/>
+      <c r="C10" s="368" t="s">
         <v>224</v>
       </c>
       <c r="D10" s="358"/>
@@ -11079,8 +11079,8 @@
       <c r="J10" s="358"/>
     </row>
     <row r="11" spans="1:10" s="21" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="367"/>
-      <c r="B11" s="369" t="s">
+      <c r="A11" s="364"/>
+      <c r="B11" s="366" t="s">
         <v>225</v>
       </c>
       <c r="C11" s="200" t="s">
@@ -11105,18 +11105,18 @@
       <c r="J11" s="202"/>
     </row>
     <row r="12" spans="1:10" s="21" customFormat="1" ht="144" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="368"/>
-      <c r="B12" s="370"/>
-      <c r="C12" s="365" t="s">
+      <c r="A12" s="365"/>
+      <c r="B12" s="367"/>
+      <c r="C12" s="369" t="s">
         <v>229</v>
       </c>
-      <c r="D12" s="366"/>
-      <c r="E12" s="366"/>
-      <c r="F12" s="366"/>
-      <c r="G12" s="366"/>
-      <c r="H12" s="366"/>
-      <c r="I12" s="366"/>
-      <c r="J12" s="366"/>
+      <c r="D12" s="370"/>
+      <c r="E12" s="370"/>
+      <c r="F12" s="370"/>
+      <c r="G12" s="370"/>
+      <c r="H12" s="370"/>
+      <c r="I12" s="370"/>
+      <c r="J12" s="370"/>
     </row>
     <row r="13" spans="1:10" s="21" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="195"/>
@@ -11145,8 +11145,8 @@
       </c>
     </row>
     <row r="14" spans="1:10" s="21" customFormat="1" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="347"/>
-      <c r="B14" s="351" t="s">
+      <c r="A14" s="330"/>
+      <c r="B14" s="334" t="s">
         <v>233</v>
       </c>
       <c r="C14" s="87" t="s">
@@ -11174,8 +11174,8 @@
     </row>
     <row r="15" spans="1:10" s="21" customFormat="1" ht="258.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="326"/>
-      <c r="B15" s="352"/>
-      <c r="C15" s="364" t="s">
+      <c r="B15" s="335"/>
+      <c r="C15" s="368" t="s">
         <v>240</v>
       </c>
       <c r="D15" s="357"/>
@@ -11228,17 +11228,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="C10:J10"/>
+    <mergeCell ref="C12:J12"/>
+    <mergeCell ref="C15:J15"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="B14:B15"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="C10:J10"/>
-    <mergeCell ref="C12:J12"/>
-    <mergeCell ref="C15:J15"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11309,11 +11309,11 @@
       <c r="F3" s="57"/>
       <c r="G3" s="57"/>
       <c r="H3" s="57"/>
-      <c r="I3" s="328" t="s">
+      <c r="I3" s="353" t="s">
         <v>130</v>
       </c>
-      <c r="J3" s="371"/>
-      <c r="K3" s="371"/>
+      <c r="J3" s="379"/>
+      <c r="K3" s="379"/>
     </row>
     <row r="4" spans="1:12" ht="47.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="58"/>
@@ -11336,18 +11336,18 @@
       <c r="H4" s="141" t="s">
         <v>243</v>
       </c>
-      <c r="I4" s="372" t="s">
+      <c r="I4" s="380" t="s">
         <v>114</v>
       </c>
-      <c r="J4" s="373"/>
-      <c r="K4" s="373"/>
+      <c r="J4" s="381"/>
+      <c r="K4" s="381"/>
       <c r="L4" s="170" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="21" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="325"/>
-      <c r="B5" s="381" t="s">
+      <c r="B5" s="377" t="s">
         <v>57</v>
       </c>
       <c r="C5" s="41" t="s">
@@ -11368,15 +11368,15 @@
       <c r="H5" s="100" t="s">
         <v>248</v>
       </c>
-      <c r="I5" s="374" t="s">
+      <c r="I5" s="382" t="s">
         <v>249</v>
       </c>
-      <c r="J5" s="375"/>
-      <c r="K5" s="375"/>
+      <c r="J5" s="383"/>
+      <c r="K5" s="383"/>
     </row>
     <row r="6" spans="1:12" s="21" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="379"/>
-      <c r="B6" s="343"/>
+      <c r="A6" s="372"/>
+      <c r="B6" s="341"/>
       <c r="C6" s="143" t="s">
         <v>250</v>
       </c>
@@ -11395,15 +11395,15 @@
       <c r="H6" s="144" t="s">
         <v>253</v>
       </c>
-      <c r="I6" s="376" t="s">
+      <c r="I6" s="384" t="s">
         <v>254</v>
       </c>
-      <c r="J6" s="340"/>
-      <c r="K6" s="340"/>
+      <c r="J6" s="351"/>
+      <c r="K6" s="351"/>
     </row>
     <row r="7" spans="1:12" s="21" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="380"/>
-      <c r="B7" s="382"/>
+      <c r="A7" s="373"/>
+      <c r="B7" s="378"/>
       <c r="C7" s="38" t="s">
         <v>255</v>
       </c>
@@ -11422,9 +11422,9 @@
       <c r="H7" s="145" t="s">
         <v>257</v>
       </c>
-      <c r="I7" s="377"/>
-      <c r="J7" s="378"/>
-      <c r="K7" s="378"/>
+      <c r="I7" s="385"/>
+      <c r="J7" s="386"/>
+      <c r="K7" s="386"/>
       <c r="L7" s="172"/>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -11488,12 +11488,12 @@
         <v>63</v>
       </c>
       <c r="J10" s="154"/>
-      <c r="K10" s="384" t="s">
+      <c r="K10" s="374" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="B11" s="379"/>
+      <c r="B11" s="372"/>
       <c r="C11" s="155">
         <v>100</v>
       </c>
@@ -11513,10 +11513,10 @@
         <v>271</v>
       </c>
       <c r="J11" s="22"/>
-      <c r="K11" s="385"/>
+      <c r="K11" s="375"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="B12" s="348"/>
+      <c r="B12" s="331"/>
       <c r="C12" s="158">
         <v>150</v>
       </c>
@@ -11543,10 +11543,10 @@
         <f t="shared" ref="J12:J38" si="1">+$J$39*($J$40^F12)</f>
         <v>1046.4197387069939</v>
       </c>
-      <c r="K12" s="385"/>
+      <c r="K12" s="375"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="B13" s="383" t="s">
+      <c r="B13" s="371" t="s">
         <v>275</v>
       </c>
       <c r="C13" s="161">
@@ -11575,10 +11575,10 @@
         <f t="shared" si="1"/>
         <v>987.69159638588894</v>
       </c>
-      <c r="K13" s="385"/>
+      <c r="K13" s="375"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="B14" s="379"/>
+      <c r="B14" s="372"/>
       <c r="C14" s="155">
         <v>100</v>
       </c>
@@ -11605,10 +11605,10 @@
         <f t="shared" si="1"/>
         <v>932.25944951757367</v>
       </c>
-      <c r="K14" s="385"/>
+      <c r="K14" s="375"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="B15" s="348"/>
+      <c r="B15" s="331"/>
       <c r="C15" s="158">
         <v>150</v>
       </c>
@@ -11635,10 +11635,10 @@
         <f t="shared" si="1"/>
         <v>879.93831717816033</v>
       </c>
-      <c r="K15" s="385"/>
+      <c r="K15" s="375"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="B16" s="383" t="s">
+      <c r="B16" s="371" t="s">
         <v>285</v>
       </c>
       <c r="C16" s="155">
@@ -11667,10 +11667,10 @@
         <f t="shared" si="1"/>
         <v>830.55360011530422</v>
       </c>
-      <c r="K16" s="385"/>
+      <c r="K16" s="375"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="B17" s="379"/>
+      <c r="B17" s="372"/>
       <c r="C17" s="155">
         <v>100</v>
       </c>
@@ -11697,10 +11697,10 @@
         <f t="shared" si="1"/>
         <v>783.94049809837475</v>
       </c>
-      <c r="K17" s="385"/>
+      <c r="K17" s="375"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="B18" s="348"/>
+      <c r="B18" s="331"/>
       <c r="C18" s="155">
         <v>150</v>
       </c>
@@ -11727,11 +11727,11 @@
         <f t="shared" si="1"/>
         <v>739.94345996863933</v>
       </c>
-      <c r="K18" s="385"/>
+      <c r="K18" s="375"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19" s="16"/>
-      <c r="B19" s="383" t="s">
+      <c r="B19" s="371" t="s">
         <v>295</v>
       </c>
       <c r="C19" s="161">
@@ -11760,10 +11760,10 @@
         <f t="shared" si="1"/>
         <v>698.4156645542439</v>
       </c>
-      <c r="K19" s="385"/>
+      <c r="K19" s="375"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="B20" s="379"/>
+      <c r="B20" s="372"/>
       <c r="C20" s="155">
         <v>100</v>
       </c>
@@ -11790,11 +11790,11 @@
         <f t="shared" si="1"/>
         <v>659.21853071776547</v>
       </c>
-      <c r="K20" s="385"/>
+      <c r="K20" s="375"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A21" s="22"/>
-      <c r="B21" s="348"/>
+      <c r="B21" s="331"/>
       <c r="C21" s="158">
         <v>150</v>
       </c>
@@ -11821,10 +11821,10 @@
         <f t="shared" si="1"/>
         <v>622.22125490133214</v>
       </c>
-      <c r="K21" s="385"/>
+      <c r="K21" s="375"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="B22" s="383" t="s">
+      <c r="B22" s="371" t="s">
         <v>304</v>
       </c>
       <c r="C22" s="155">
@@ -11853,10 +11853,10 @@
         <f t="shared" si="1"/>
         <v>587.30037462606617</v>
       </c>
-      <c r="K22" s="385"/>
+      <c r="K22" s="375"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="B23" s="379"/>
+      <c r="B23" s="372"/>
       <c r="C23" s="155">
         <v>100</v>
       </c>
@@ -11883,10 +11883,10 @@
         <f t="shared" si="1"/>
         <v>554.33935648921727</v>
       </c>
-      <c r="K23" s="385"/>
+      <c r="K23" s="375"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="B24" s="348"/>
+      <c r="B24" s="331"/>
       <c r="C24" s="155">
         <v>150</v>
       </c>
@@ -11913,10 +11913,10 @@
         <f t="shared" si="1"/>
         <v>523.22820728410431</v>
       </c>
-      <c r="K24" s="385"/>
+      <c r="K24" s="375"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="B25" s="383" t="s">
+      <c r="B25" s="371" t="s">
         <v>313</v>
       </c>
       <c r="C25" s="161">
@@ -11945,10 +11945,10 @@
         <f t="shared" si="1"/>
         <v>493.86310694514589</v>
       </c>
-      <c r="K25" s="385"/>
+      <c r="K25" s="375"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="B26" s="379"/>
+      <c r="B26" s="372"/>
       <c r="C26" s="155">
         <v>100</v>
       </c>
@@ -11975,10 +11975,10 @@
         <f t="shared" si="1"/>
         <v>466.14606209309068</v>
       </c>
-      <c r="K26" s="385"/>
+      <c r="K26" s="375"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="B27" s="348"/>
+      <c r="B27" s="331"/>
       <c r="C27" s="158">
         <v>150</v>
       </c>
@@ -12005,10 +12005,10 @@
         <f t="shared" si="1"/>
         <v>439.98457902430545</v>
       </c>
-      <c r="K27" s="385"/>
+      <c r="K27" s="375"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="B28" s="383" t="s">
+      <c r="B28" s="371" t="s">
         <v>319</v>
       </c>
       <c r="C28" s="155">
@@ -12037,10 +12037,10 @@
         <f t="shared" si="1"/>
         <v>415.29135505286217</v>
       </c>
-      <c r="K28" s="385"/>
+      <c r="K28" s="375"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="B29" s="379"/>
+      <c r="B29" s="372"/>
       <c r="C29" s="155">
         <v>100</v>
       </c>
@@ -12067,10 +12067,10 @@
         <f t="shared" si="1"/>
         <v>391.9839871754121</v>
       </c>
-      <c r="K29" s="385"/>
+      <c r="K29" s="375"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="B30" s="380"/>
+      <c r="B30" s="373"/>
       <c r="C30" s="165">
         <v>150</v>
       </c>
@@ -12097,7 +12097,7 @@
         <f t="shared" si="1"/>
         <v>369.98469708664038</v>
       </c>
-      <c r="K30" s="385"/>
+      <c r="K30" s="375"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.4">
       <c r="E31" s="3" t="s">
@@ -12119,7 +12119,7 @@
         <f t="shared" si="1"/>
         <v>349.22007162765976</v>
       </c>
-      <c r="K31" s="385"/>
+      <c r="K31" s="375"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.4">
       <c r="B32" s="53"/>
@@ -12142,7 +12142,7 @@
         <f t="shared" si="1"/>
         <v>329.6208178012003</v>
       </c>
-      <c r="K32" s="385"/>
+      <c r="K32" s="375"/>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B33" s="53"/>
@@ -12162,7 +12162,7 @@
         <f t="shared" si="1"/>
         <v>311.12153153606579</v>
       </c>
-      <c r="K33" s="385"/>
+      <c r="K33" s="375"/>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B34" s="53"/>
@@ -12182,7 +12182,7 @@
         <f t="shared" si="1"/>
         <v>293.66047942920522</v>
       </c>
-      <c r="K34" s="385"/>
+      <c r="K34" s="375"/>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.4">
       <c r="F35" s="162">
@@ -12201,7 +12201,7 @@
         <f t="shared" si="1"/>
         <v>277.17939273705963</v>
       </c>
-      <c r="K35" s="385"/>
+      <c r="K35" s="375"/>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.4">
       <c r="F36" s="162">
@@ -12220,7 +12220,7 @@
         <f t="shared" si="1"/>
         <v>261.623272928718</v>
       </c>
-      <c r="K36" s="385"/>
+      <c r="K36" s="375"/>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.4">
       <c r="F37" s="162">
@@ -12239,7 +12239,7 @@
         <f t="shared" si="1"/>
         <v>246.94020815200005</v>
       </c>
-      <c r="K37" s="385"/>
+      <c r="K37" s="375"/>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.4">
       <c r="F38" s="162">
@@ -12258,7 +12258,7 @@
         <f t="shared" si="1"/>
         <v>233.08120000000002</v>
       </c>
-      <c r="K38" s="385"/>
+      <c r="K38" s="375"/>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.4">
       <c r="F39" s="162">
@@ -12276,7 +12276,7 @@
       <c r="J39" s="160">
         <v>220</v>
       </c>
-      <c r="K39" s="386"/>
+      <c r="K39" s="376"/>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.4">
       <c r="F40" s="166" t="s">
@@ -12297,21 +12297,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="B16:B18"/>
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="B22:B24"/>
     <mergeCell ref="B25:B27"/>
     <mergeCell ref="B28:B30"/>
     <mergeCell ref="K10:K39"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I7:K7"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12368,10 +12368,10 @@
       <c r="E3" s="57"/>
       <c r="F3" s="57"/>
       <c r="G3" s="57"/>
-      <c r="H3" s="387" t="s">
+      <c r="H3" s="421" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="371"/>
+      <c r="I3" s="379"/>
     </row>
     <row r="4" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="58"/>
@@ -12400,7 +12400,7 @@
     </row>
     <row r="5" spans="1:9" s="79" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="82"/>
-      <c r="B5" s="410" t="s">
+      <c r="B5" s="392" t="s">
         <v>350</v>
       </c>
       <c r="C5" s="83" t="s">
@@ -12421,20 +12421,20 @@
     </row>
     <row r="6" spans="1:9" s="79" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="86"/>
-      <c r="B6" s="370"/>
-      <c r="C6" s="388" t="s">
+      <c r="B6" s="367"/>
+      <c r="C6" s="422" t="s">
         <v>353</v>
       </c>
-      <c r="D6" s="389"/>
-      <c r="E6" s="389"/>
-      <c r="F6" s="389"/>
-      <c r="G6" s="389"/>
-      <c r="H6" s="389"/>
-      <c r="I6" s="390"/>
+      <c r="D6" s="412"/>
+      <c r="E6" s="412"/>
+      <c r="F6" s="412"/>
+      <c r="G6" s="412"/>
+      <c r="H6" s="412"/>
+      <c r="I6" s="413"/>
     </row>
     <row r="7" spans="1:9" s="21" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="402"/>
-      <c r="B7" s="411" t="s">
+      <c r="A7" s="405"/>
+      <c r="B7" s="393" t="s">
         <v>87</v>
       </c>
       <c r="C7" s="87" t="s">
@@ -12458,9 +12458,9 @@
       <c r="I7" s="130"/>
     </row>
     <row r="8" spans="1:9" s="21" customFormat="1" ht="86.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="403"/>
-      <c r="B8" s="412"/>
-      <c r="C8" s="364" t="s">
+      <c r="A8" s="406"/>
+      <c r="B8" s="394"/>
+      <c r="C8" s="368" t="s">
         <v>359</v>
       </c>
       <c r="D8" s="357"/>
@@ -12468,11 +12468,11 @@
       <c r="F8" s="357"/>
       <c r="G8" s="357"/>
       <c r="H8" s="358"/>
-      <c r="I8" s="391"/>
+      <c r="I8" s="420"/>
     </row>
     <row r="9" spans="1:9" s="21" customFormat="1" ht="64.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="404"/>
-      <c r="B9" s="413" t="s">
+      <c r="A9" s="407"/>
+      <c r="B9" s="395" t="s">
         <v>360</v>
       </c>
       <c r="C9" s="87" t="s">
@@ -12496,9 +12496,9 @@
       <c r="I9" s="130"/>
     </row>
     <row r="10" spans="1:9" s="21" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="403"/>
-      <c r="B10" s="412"/>
-      <c r="C10" s="364" t="s">
+      <c r="A10" s="406"/>
+      <c r="B10" s="394"/>
+      <c r="C10" s="368" t="s">
         <v>366</v>
       </c>
       <c r="D10" s="357"/>
@@ -12506,11 +12506,11 @@
       <c r="F10" s="357"/>
       <c r="G10" s="357"/>
       <c r="H10" s="357"/>
-      <c r="I10" s="392"/>
+      <c r="I10" s="419"/>
     </row>
     <row r="11" spans="1:9" s="21" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="405"/>
-      <c r="B11" s="414" t="s">
+      <c r="A11" s="404"/>
+      <c r="B11" s="396" t="s">
         <v>83</v>
       </c>
       <c r="C11" s="87" t="s">
@@ -12533,8 +12533,8 @@
     </row>
     <row r="12" spans="1:9" s="21" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="326"/>
-      <c r="B12" s="412"/>
-      <c r="C12" s="364" t="s">
+      <c r="B12" s="394"/>
+      <c r="C12" s="368" t="s">
         <v>370</v>
       </c>
       <c r="D12" s="357"/>
@@ -12542,11 +12542,11 @@
       <c r="F12" s="357"/>
       <c r="G12" s="357"/>
       <c r="H12" s="357"/>
-      <c r="I12" s="392"/>
+      <c r="I12" s="419"/>
     </row>
     <row r="13" spans="1:9" s="21" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="404"/>
-      <c r="B13" s="413" t="s">
+      <c r="A13" s="407"/>
+      <c r="B13" s="395" t="s">
         <v>371</v>
       </c>
       <c r="C13" s="87" t="s">
@@ -12568,9 +12568,9 @@
       <c r="I13" s="130"/>
     </row>
     <row r="14" spans="1:9" s="21" customFormat="1" ht="138.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="403"/>
-      <c r="B14" s="412"/>
-      <c r="C14" s="364" t="s">
+      <c r="A14" s="406"/>
+      <c r="B14" s="394"/>
+      <c r="C14" s="368" t="s">
         <v>375</v>
       </c>
       <c r="D14" s="357"/>
@@ -12578,7 +12578,7 @@
       <c r="F14" s="357"/>
       <c r="G14" s="357"/>
       <c r="H14" s="357"/>
-      <c r="I14" s="392"/>
+      <c r="I14" s="419"/>
     </row>
     <row r="15" spans="1:9" s="21" customFormat="1" ht="85.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="92"/>
@@ -12648,8 +12648,8 @@
       <c r="I17" s="133"/>
     </row>
     <row r="18" spans="1:9" s="21" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="347"/>
-      <c r="B18" s="413" t="s">
+      <c r="A18" s="330"/>
+      <c r="B18" s="395" t="s">
         <v>384</v>
       </c>
       <c r="C18" s="102" t="s">
@@ -12674,8 +12674,8 @@
     </row>
     <row r="19" spans="1:9" s="21" customFormat="1" ht="58.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="326"/>
-      <c r="B19" s="352"/>
-      <c r="C19" s="364" t="s">
+      <c r="B19" s="335"/>
+      <c r="C19" s="368" t="s">
         <v>389</v>
       </c>
       <c r="D19" s="357"/>
@@ -12683,11 +12683,11 @@
       <c r="F19" s="357"/>
       <c r="G19" s="357"/>
       <c r="H19" s="357"/>
-      <c r="I19" s="392"/>
+      <c r="I19" s="419"/>
     </row>
     <row r="20" spans="1:9" s="21" customFormat="1" ht="85.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="347"/>
-      <c r="B20" s="414" t="s">
+      <c r="A20" s="330"/>
+      <c r="B20" s="396" t="s">
         <v>390</v>
       </c>
       <c r="C20" s="106" t="s">
@@ -12710,8 +12710,8 @@
     </row>
     <row r="21" spans="1:9" s="21" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="326"/>
-      <c r="B21" s="412"/>
-      <c r="C21" s="364" t="s">
+      <c r="B21" s="394"/>
+      <c r="C21" s="368" t="s">
         <v>394</v>
       </c>
       <c r="D21" s="357"/>
@@ -12719,11 +12719,11 @@
       <c r="F21" s="357"/>
       <c r="G21" s="357"/>
       <c r="H21" s="358"/>
-      <c r="I21" s="391"/>
+      <c r="I21" s="420"/>
     </row>
     <row r="22" spans="1:9" s="80" customFormat="1" ht="138" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="405"/>
-      <c r="B22" s="351" t="s">
+      <c r="A22" s="404"/>
+      <c r="B22" s="334" t="s">
         <v>395</v>
       </c>
       <c r="C22" s="87" t="s">
@@ -12744,8 +12744,8 @@
     </row>
     <row r="23" spans="1:9" s="80" customFormat="1" ht="115.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="326"/>
-      <c r="B23" s="352"/>
-      <c r="C23" s="364" t="s">
+      <c r="B23" s="335"/>
+      <c r="C23" s="368" t="s">
         <v>397</v>
       </c>
       <c r="D23" s="357"/>
@@ -12753,11 +12753,11 @@
       <c r="F23" s="357"/>
       <c r="G23" s="357"/>
       <c r="H23" s="357"/>
-      <c r="I23" s="392"/>
+      <c r="I23" s="419"/>
     </row>
     <row r="24" spans="1:9" s="80" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="405"/>
-      <c r="B24" s="351" t="s">
+      <c r="A24" s="404"/>
+      <c r="B24" s="334" t="s">
         <v>398</v>
       </c>
       <c r="C24" s="87" t="s">
@@ -12780,8 +12780,8 @@
     </row>
     <row r="25" spans="1:9" s="80" customFormat="1" ht="127.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="326"/>
-      <c r="B25" s="352"/>
-      <c r="C25" s="364" t="s">
+      <c r="B25" s="335"/>
+      <c r="C25" s="368" t="s">
         <v>401</v>
       </c>
       <c r="D25" s="357"/>
@@ -12789,7 +12789,7 @@
       <c r="F25" s="357"/>
       <c r="G25" s="357"/>
       <c r="H25" s="357"/>
-      <c r="I25" s="392"/>
+      <c r="I25" s="419"/>
     </row>
     <row r="26" spans="1:9" s="21" customFormat="1" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="109"/>
@@ -12813,8 +12813,8 @@
       <c r="I26" s="113"/>
     </row>
     <row r="27" spans="1:9" s="52" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="406"/>
-      <c r="B27" s="415" t="s">
+      <c r="A27" s="388"/>
+      <c r="B27" s="397" t="s">
         <v>403</v>
       </c>
       <c r="C27" s="114" t="s">
@@ -12834,21 +12834,21 @@
       <c r="I27" s="136"/>
     </row>
     <row r="28" spans="1:9" s="52" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="368"/>
-      <c r="B28" s="370"/>
-      <c r="C28" s="393" t="s">
+      <c r="A28" s="365"/>
+      <c r="B28" s="367"/>
+      <c r="C28" s="408" t="s">
         <v>405</v>
       </c>
-      <c r="D28" s="394"/>
-      <c r="E28" s="394"/>
-      <c r="F28" s="394"/>
-      <c r="G28" s="394"/>
+      <c r="D28" s="409"/>
+      <c r="E28" s="409"/>
+      <c r="F28" s="409"/>
+      <c r="G28" s="409"/>
       <c r="H28" s="118"/>
       <c r="I28" s="137"/>
     </row>
     <row r="29" spans="1:9" s="52" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="406"/>
-      <c r="B29" s="416" t="s">
+      <c r="A29" s="388"/>
+      <c r="B29" s="398" t="s">
         <v>406</v>
       </c>
       <c r="C29" s="119" t="s">
@@ -12868,21 +12868,21 @@
       <c r="I29" s="138"/>
     </row>
     <row r="30" spans="1:9" s="52" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="368"/>
-      <c r="B30" s="417"/>
-      <c r="C30" s="395" t="s">
+      <c r="A30" s="365"/>
+      <c r="B30" s="399"/>
+      <c r="C30" s="410" t="s">
         <v>408</v>
       </c>
-      <c r="D30" s="394"/>
-      <c r="E30" s="394"/>
-      <c r="F30" s="394"/>
-      <c r="G30" s="394"/>
-      <c r="H30" s="394"/>
-      <c r="I30" s="396"/>
+      <c r="D30" s="409"/>
+      <c r="E30" s="409"/>
+      <c r="F30" s="409"/>
+      <c r="G30" s="409"/>
+      <c r="H30" s="409"/>
+      <c r="I30" s="411"/>
     </row>
     <row r="31" spans="1:9" s="52" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="406"/>
-      <c r="B31" s="418" t="s">
+      <c r="A31" s="388"/>
+      <c r="B31" s="400" t="s">
         <v>17</v>
       </c>
       <c r="C31" s="120" t="s">
@@ -12902,21 +12902,21 @@
       <c r="I31" s="138"/>
     </row>
     <row r="32" spans="1:9" s="52" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="368"/>
-      <c r="B32" s="419"/>
-      <c r="C32" s="395" t="s">
+      <c r="A32" s="365"/>
+      <c r="B32" s="401"/>
+      <c r="C32" s="410" t="s">
         <v>410</v>
       </c>
-      <c r="D32" s="389"/>
-      <c r="E32" s="389"/>
-      <c r="F32" s="389"/>
-      <c r="G32" s="389"/>
-      <c r="H32" s="389"/>
-      <c r="I32" s="390"/>
+      <c r="D32" s="412"/>
+      <c r="E32" s="412"/>
+      <c r="F32" s="412"/>
+      <c r="G32" s="412"/>
+      <c r="H32" s="412"/>
+      <c r="I32" s="413"/>
     </row>
     <row r="33" spans="1:9" s="81" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="407"/>
-      <c r="B33" s="420" t="s">
+      <c r="A33" s="389"/>
+      <c r="B33" s="402" t="s">
         <v>411</v>
       </c>
       <c r="C33" s="125" t="s">
@@ -12938,21 +12938,21 @@
       <c r="I33" s="139"/>
     </row>
     <row r="34" spans="1:9" s="81" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="408"/>
-      <c r="B34" s="421"/>
-      <c r="C34" s="397" t="s">
+      <c r="A34" s="390"/>
+      <c r="B34" s="403"/>
+      <c r="C34" s="414" t="s">
         <v>415</v>
       </c>
-      <c r="D34" s="398"/>
-      <c r="E34" s="398"/>
-      <c r="F34" s="398"/>
-      <c r="G34" s="398"/>
-      <c r="H34" s="398"/>
-      <c r="I34" s="399"/>
+      <c r="D34" s="415"/>
+      <c r="E34" s="415"/>
+      <c r="F34" s="415"/>
+      <c r="G34" s="415"/>
+      <c r="H34" s="415"/>
+      <c r="I34" s="416"/>
     </row>
     <row r="35" spans="1:9" s="52" customFormat="1" ht="117.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="409"/>
-      <c r="B35" s="422" t="s">
+      <c r="A35" s="391"/>
+      <c r="B35" s="387" t="s">
         <v>416</v>
       </c>
       <c r="C35" s="72" t="s">
@@ -12977,16 +12977,16 @@
     </row>
     <row r="36" spans="1:9" s="52" customFormat="1" ht="189" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="326"/>
-      <c r="B36" s="354"/>
-      <c r="C36" s="364" t="s">
+      <c r="B36" s="337"/>
+      <c r="C36" s="368" t="s">
         <v>421</v>
       </c>
-      <c r="D36" s="400"/>
-      <c r="E36" s="400"/>
-      <c r="F36" s="400"/>
-      <c r="G36" s="400"/>
-      <c r="H36" s="400"/>
-      <c r="I36" s="401"/>
+      <c r="D36" s="417"/>
+      <c r="E36" s="417"/>
+      <c r="F36" s="417"/>
+      <c r="G36" s="417"/>
+      <c r="H36" s="417"/>
+      <c r="I36" s="418"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A37" s="74"/>
@@ -13025,6 +13025,32 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="C6:I6"/>
+    <mergeCell ref="C8:I8"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="C12:I12"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="C19:I19"/>
+    <mergeCell ref="C21:I21"/>
+    <mergeCell ref="C23:I23"/>
+    <mergeCell ref="C25:I25"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C30:I30"/>
+    <mergeCell ref="C32:I32"/>
+    <mergeCell ref="C34:I34"/>
+    <mergeCell ref="C36:I36"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A29:A30"/>
     <mergeCell ref="B35:B36"/>
     <mergeCell ref="A31:A32"/>
     <mergeCell ref="A33:A34"/>
@@ -13041,32 +13067,6 @@
     <mergeCell ref="B27:B28"/>
     <mergeCell ref="B29:B30"/>
     <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C30:I30"/>
-    <mergeCell ref="C32:I32"/>
-    <mergeCell ref="C34:I34"/>
-    <mergeCell ref="C36:I36"/>
-    <mergeCell ref="C14:I14"/>
-    <mergeCell ref="C19:I19"/>
-    <mergeCell ref="C21:I21"/>
-    <mergeCell ref="C23:I23"/>
-    <mergeCell ref="C25:I25"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="C6:I6"/>
-    <mergeCell ref="C8:I8"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="C12:I12"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13124,10 +13124,10 @@
       <c r="E3" s="57"/>
       <c r="F3" s="57"/>
       <c r="G3" s="57"/>
-      <c r="H3" s="387" t="s">
+      <c r="H3" s="421" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="371"/>
+      <c r="I3" s="379"/>
     </row>
     <row r="4" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="58"/>
@@ -13155,7 +13155,7 @@
       </c>
     </row>
     <row r="5" spans="1:9" s="52" customFormat="1" ht="97.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="409"/>
+      <c r="A5" s="391"/>
       <c r="B5" s="423" t="s">
         <v>424</v>
       </c>
@@ -13181,16 +13181,16 @@
     </row>
     <row r="6" spans="1:9" s="52" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="326"/>
-      <c r="B6" s="352"/>
-      <c r="C6" s="364" t="s">
+      <c r="B6" s="335"/>
+      <c r="C6" s="368" t="s">
         <v>428</v>
       </c>
-      <c r="D6" s="400"/>
-      <c r="E6" s="400"/>
-      <c r="F6" s="400"/>
-      <c r="G6" s="400"/>
-      <c r="H6" s="400"/>
-      <c r="I6" s="401"/>
+      <c r="D6" s="417"/>
+      <c r="E6" s="417"/>
+      <c r="F6" s="417"/>
+      <c r="G6" s="417"/>
+      <c r="H6" s="417"/>
+      <c r="I6" s="418"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A7" s="74"/>
@@ -13288,10 +13288,10 @@
       <c r="E3" s="57"/>
       <c r="F3" s="57"/>
       <c r="G3" s="57"/>
-      <c r="H3" s="387" t="s">
+      <c r="H3" s="421" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="371"/>
+      <c r="I3" s="379"/>
     </row>
     <row r="4" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="58"/>
@@ -13319,7 +13319,7 @@
       </c>
     </row>
     <row r="5" spans="1:9" s="52" customFormat="1" ht="101.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="409"/>
+      <c r="A5" s="391"/>
       <c r="B5" s="423" t="s">
         <v>433</v>
       </c>
@@ -13345,19 +13345,19 @@
     </row>
     <row r="6" spans="1:9" s="52" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="326"/>
-      <c r="B6" s="352"/>
-      <c r="C6" s="364" t="s">
+      <c r="B6" s="335"/>
+      <c r="C6" s="368" t="s">
         <v>437</v>
       </c>
-      <c r="D6" s="400"/>
-      <c r="E6" s="400"/>
-      <c r="F6" s="400"/>
-      <c r="G6" s="400"/>
-      <c r="H6" s="400"/>
-      <c r="I6" s="401"/>
+      <c r="D6" s="417"/>
+      <c r="E6" s="417"/>
+      <c r="F6" s="417"/>
+      <c r="G6" s="417"/>
+      <c r="H6" s="417"/>
+      <c r="I6" s="418"/>
     </row>
     <row r="7" spans="1:9" s="52" customFormat="1" ht="144" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="409"/>
+      <c r="A7" s="391"/>
       <c r="B7" s="423" t="s">
         <v>438</v>
       </c>
@@ -13385,16 +13385,16 @@
     </row>
     <row r="8" spans="1:9" s="52" customFormat="1" ht="150.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="326"/>
-      <c r="B8" s="352"/>
-      <c r="C8" s="364" t="s">
+      <c r="B8" s="335"/>
+      <c r="C8" s="368" t="s">
         <v>443</v>
       </c>
-      <c r="D8" s="400"/>
-      <c r="E8" s="400"/>
-      <c r="F8" s="400"/>
-      <c r="G8" s="400"/>
-      <c r="H8" s="400"/>
-      <c r="I8" s="401"/>
+      <c r="D8" s="417"/>
+      <c r="E8" s="417"/>
+      <c r="F8" s="417"/>
+      <c r="G8" s="417"/>
+      <c r="H8" s="417"/>
+      <c r="I8" s="418"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B9" s="43" t="s">
